--- a/main/ig/StructureDefinition-fr-lm-organisation.xlsx
+++ b/main/ig/StructureDefinition-fr-lm-organisation.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-18T14:11:29+00:00</t>
+    <t>2026-05-21T09:18:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-lm-organisation.xlsx
+++ b/main/ig/StructureDefinition-fr-lm-organisation.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-21T09:18:21+00:00</t>
+    <t>2026-06-01T14:41:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-lm-organisation.xlsx
+++ b/main/ig/StructureDefinition-fr-lm-organisation.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-01T14:41:15+00:00</t>
+    <t>2026-06-01T15:18:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-lm-organisation.xlsx
+++ b/main/ig/StructureDefinition-fr-lm-organisation.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-01T15:18:33+00:00</t>
+    <t>2026-06-02T07:35:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-lm-organisation.xlsx
+++ b/main/ig/StructureDefinition-fr-lm-organisation.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-02T07:35:19+00:00</t>
+    <t>2026-06-04T15:31:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-lm-organisation.xlsx
+++ b/main/ig/StructureDefinition-fr-lm-organisation.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-04T15:31:02+00:00</t>
+    <t>2026-06-16T14:27:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -237,10 +237,7 @@
     <t/>
   </si>
   <si>
-    <t>0</t>
-  </si>
-  <si>
-    <t>*</t>
+    <t>1</t>
   </si>
   <si>
     <t xml:space="preserve">
@@ -250,6 +247,12 @@
     <t>Base</t>
   </si>
   <si>
+    <t>0</t>
+  </si>
+  <si>
+    <t>*</t>
+  </si>
+  <si>
     <t>fr-lm-organisation.identifier</t>
   </si>
   <si>
@@ -277,9 +280,6 @@
   </si>
   <si>
     <t>fr-lm-organisation.name</t>
-  </si>
-  <si>
-    <t>1</t>
   </si>
   <si>
     <t xml:space="preserve">string
@@ -796,19 +796,19 @@
         <v>74</v>
       </c>
       <c r="G2" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="H2" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="I2" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="J2" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="K2" t="s" s="2">
         <v>75</v>
-      </c>
-      <c r="H2" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="I2" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="J2" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="K2" t="s" s="2">
-        <v>76</v>
       </c>
       <c r="L2" t="s" s="2">
         <v>9</v>
@@ -865,13 +865,13 @@
         <v>73</v>
       </c>
       <c r="AF2" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AG2" t="s" s="2">
         <v>77</v>
       </c>
-      <c r="AG2" t="s" s="2">
-        <v>74</v>
-      </c>
       <c r="AH2" t="s" s="2">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="AI2" t="s" s="2">
         <v>73</v>
@@ -882,10 +882,10 @@
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C3" s="2"/>
       <c r="D3" t="s" s="2">
@@ -893,10 +893,10 @@
       </c>
       <c r="E3" s="2"/>
       <c r="F3" t="s" s="2">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="G3" t="s" s="2">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="H3" t="s" s="2">
         <v>73</v>
@@ -908,13 +908,13 @@
         <v>73</v>
       </c>
       <c r="K3" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="L3" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="M3" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="N3" s="2"/>
       <c r="O3" s="2"/>
@@ -965,13 +965,13 @@
         <v>73</v>
       </c>
       <c r="AF3" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AG3" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AH3" t="s" s="2">
         <v>78</v>
-      </c>
-      <c r="AG3" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AH3" t="s" s="2">
-        <v>75</v>
       </c>
       <c r="AI3" t="s" s="2">
         <v>73</v>
@@ -982,10 +982,10 @@
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C4" s="2"/>
       <c r="D4" t="s" s="2">
@@ -993,10 +993,10 @@
       </c>
       <c r="E4" s="2"/>
       <c r="F4" t="s" s="2">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="G4" t="s" s="2">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="H4" t="s" s="2">
         <v>73</v>
@@ -1008,13 +1008,13 @@
         <v>73</v>
       </c>
       <c r="K4" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="L4" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="M4" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="N4" s="2"/>
       <c r="O4" s="2"/>
@@ -1044,10 +1044,10 @@
         <v>73</v>
       </c>
       <c r="Y4" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="Z4" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="AA4" t="s" s="2">
         <v>73</v>
@@ -1065,13 +1065,13 @@
         <v>73</v>
       </c>
       <c r="AF4" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AG4" t="s" s="2">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="AH4" t="s" s="2">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="AI4" t="s" s="2">
         <v>73</v>
@@ -1082,10 +1082,10 @@
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C5" s="2"/>
       <c r="D5" t="s" s="2">
@@ -1093,10 +1093,10 @@
       </c>
       <c r="E5" s="2"/>
       <c r="F5" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="G5" t="s" s="2">
         <v>74</v>
-      </c>
-      <c r="G5" t="s" s="2">
-        <v>87</v>
       </c>
       <c r="H5" t="s" s="2">
         <v>73</v>
@@ -1165,13 +1165,13 @@
         <v>73</v>
       </c>
       <c r="AF5" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="AG5" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AH5" t="s" s="2">
         <v>74</v>
-      </c>
-      <c r="AH5" t="s" s="2">
-        <v>87</v>
       </c>
       <c r="AI5" t="s" s="2">
         <v>73</v>
@@ -1193,10 +1193,10 @@
       </c>
       <c r="E6" s="2"/>
       <c r="F6" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="G6" t="s" s="2">
         <v>74</v>
-      </c>
-      <c r="G6" t="s" s="2">
-        <v>87</v>
       </c>
       <c r="H6" t="s" s="2">
         <v>73</v>
@@ -1268,10 +1268,10 @@
         <v>90</v>
       </c>
       <c r="AG6" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AH6" t="s" s="2">
         <v>74</v>
-      </c>
-      <c r="AH6" t="s" s="2">
-        <v>87</v>
       </c>
       <c r="AI6" t="s" s="2">
         <v>73</v>
@@ -1293,10 +1293,10 @@
       </c>
       <c r="E7" s="2"/>
       <c r="F7" t="s" s="2">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="G7" t="s" s="2">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="H7" t="s" s="2">
         <v>73</v>
@@ -1368,10 +1368,10 @@
         <v>93</v>
       </c>
       <c r="AG7" t="s" s="2">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="AH7" t="s" s="2">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="AI7" t="s" s="2">
         <v>73</v>
@@ -1393,10 +1393,10 @@
       </c>
       <c r="E8" s="2"/>
       <c r="F8" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="G8" t="s" s="2">
         <v>74</v>
-      </c>
-      <c r="G8" t="s" s="2">
-        <v>87</v>
       </c>
       <c r="H8" t="s" s="2">
         <v>73</v>
@@ -1468,10 +1468,10 @@
         <v>96</v>
       </c>
       <c r="AG8" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AH8" t="s" s="2">
         <v>74</v>
-      </c>
-      <c r="AH8" t="s" s="2">
-        <v>87</v>
       </c>
       <c r="AI8" t="s" s="2">
         <v>73</v>
@@ -1493,11 +1493,11 @@
       </c>
       <c r="E9" s="2"/>
       <c r="F9" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="G9" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="G9" t="s" s="2">
-        <v>87</v>
-      </c>
       <c r="H9" t="s" s="2">
         <v>73</v>
       </c>
@@ -1508,7 +1508,7 @@
         <v>73</v>
       </c>
       <c r="K9" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="L9" t="s" s="2">
         <v>100</v>
@@ -1568,10 +1568,10 @@
         <v>99</v>
       </c>
       <c r="AG9" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AH9" t="s" s="2">
         <v>74</v>
-      </c>
-      <c r="AH9" t="s" s="2">
-        <v>87</v>
       </c>
       <c r="AI9" t="s" s="2">
         <v>73</v>

--- a/main/ig/StructureDefinition-fr-lm-organisation.xlsx
+++ b/main/ig/StructureDefinition-fr-lm-organisation.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-16T14:27:29+00:00</t>
+    <t>2026-06-18T14:40:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-lm-organisation.xlsx
+++ b/main/ig/StructureDefinition-fr-lm-organisation.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-18T14:40:49+00:00</t>
+    <t>2026-06-22T09:35:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
